--- a/public/templates/RadiographyFixed_Template_WithTimer.xlsx
+++ b/public/templates/RadiographyFixed_Template_WithTimer.xlsx
@@ -1215,7 +1215,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>mA Station 1</v>
+        <v>mAs Station 1</v>
       </c>
       <c r="B30" t="str">
         <v>50</v>
@@ -1247,7 +1247,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>mA Station 2</v>
+        <v>mAs Station 2</v>
       </c>
       <c r="B31" t="str">
         <v>100</v>
@@ -1279,7 +1279,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>mA Station 3</v>
+        <v>mAs Station 3</v>
       </c>
       <c r="B32" t="str">
         <v>23</v>
